--- a/Tally_Uploads/KISHORE_FABRICS_PVT_LTD_E_SUR-10109.xlsx
+++ b/Tally_Uploads/KISHORE_FABRICS_PVT_LTD_E_SUR-10109.xlsx
@@ -596,7 +596,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>10-12-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+919949947080</t>
+          <t>+91-9949947080</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -698,10 +698,10 @@
         <v>120</v>
       </c>
       <c r="AB2" t="n">
-        <v>164.85</v>
+        <v>165.35</v>
       </c>
       <c r="AC2" t="n">
-        <v>164.85</v>
+        <v>165.35</v>
       </c>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>10-12-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -801,10 +801,10 @@
       </c>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
-        <v>126</v>
+        <v>126.38</v>
       </c>
       <c r="AC3" t="n">
-        <v>126</v>
+        <v>126.38</v>
       </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>10-12-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -898,10 +898,10 @@
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>159.25</v>
+        <v>159.73</v>
       </c>
       <c r="AC4" t="n">
-        <v>159.25</v>
+        <v>159.73</v>
       </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
@@ -925,7 +925,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>10-12-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -995,10 +995,10 @@
       </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>68.5</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>68.5</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>10-12-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1092,10 +1092,10 @@
       </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="n">
-        <v>138</v>
+        <v>138.42</v>
       </c>
       <c r="AC6" t="n">
-        <v>138</v>
+        <v>138.42</v>
       </c>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>10-12-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1189,10 +1189,10 @@
       </c>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="n">
-        <v>255.38</v>
+        <v>256.14</v>
       </c>
       <c r="AC7" t="n">
-        <v>255.38</v>
+        <v>256.14</v>
       </c>
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr"/>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>10-12-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1286,10 +1286,10 @@
       </c>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="n">
-        <v>63</v>
+        <v>63.19</v>
       </c>
       <c r="AC8" t="n">
-        <v>63</v>
+        <v>63.19</v>
       </c>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr"/>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>10-12-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1383,10 +1383,10 @@
       </c>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="n">
-        <v>24</v>
+        <v>24.06</v>
       </c>
       <c r="AC9" t="n">
-        <v>24</v>
+        <v>24.06</v>
       </c>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr"/>
